--- a/data/file_generation/reference/data_77/各小时订单数量统计_res.xlsx
+++ b/data/file_generation/reference/data_77/各小时订单数量统计_res.xlsx
@@ -1345,26 +1345,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1088785-AE1D-4BC2-B406-D9A0F95F1B17}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A8B5D80-6CBA-4A8D-AE63-D8D1279A1495}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86E751C1-9911-4E81-A13D-21F5C8A739DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70DDBE9E-B558-4B84-88CA-E0181AB46C13}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9143A0B9-D22B-4E53-A60A-FAEA58A523B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F24855AD-5EA9-47DC-A5C8-62166D7D7CDD}"/>
 </file>